--- a/data/trans_orig/IP07C03-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C03-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>13281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23335</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15493</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24560</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31763</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45420</t>
+          <t>45477</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,6%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24154</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>10371</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19619</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26903</t>
+          <t>26768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40871</t>
+          <t>41264</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,99%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>730</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19756</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35955</t>
+          <t>36926</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16985</t>
+          <t>17368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>14393</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26869</t>
+          <t>26257</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17061</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>16836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28242</t>
+          <t>27643</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>27637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42017</t>
+          <t>41749</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18043</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17741</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29650</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31202</t>
+          <t>30253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45323</t>
+          <t>45565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,87%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9176</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33821</t>
+          <t>34869</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49073</t>
+          <t>48844</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35556</t>
+          <t>36087</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50756</t>
+          <t>50586</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74940</t>
+          <t>74735</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95689</t>
+          <t>94833</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,81%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46177</t>
+          <t>45292</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27771</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42418</t>
+          <t>42605</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63295</t>
+          <t>63693</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83823</t>
+          <t>84284</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,49%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>12139</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21960</t>
+          <t>22673</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33263</t>
+          <t>33117</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24924</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>38036</t>
+          <t>37931</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49388</t>
+          <t>50698</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>67516</t>
+          <t>67359</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,91%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22953</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21158</t>
+          <t>21624</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33758</t>
+          <t>34463</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37291</t>
+          <t>36691</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54692</t>
+          <t>53237</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>48,14%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12767</t>
+          <t>12625</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20659</t>
+          <t>20716</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26891</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>40110</t>
+          <t>40633</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>58,29%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13454</t>
+          <t>13385</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23331</t>
+          <t>23136</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16807</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>23943</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>37120</t>
+          <t>37168</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>531</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>572</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>119894</t>
+          <t>118361</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>145779</t>
+          <t>144428</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>136969</t>
+          <t>135581</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>162945</t>
+          <t>162236</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>263531</t>
+          <t>263082</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>300112</t>
+          <t>301662</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>102271</t>
+          <t>102352</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>127606</t>
+          <t>128418</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>112909</t>
+          <t>113191</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>138829</t>
+          <t>140258</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>222633</t>
+          <t>220831</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>259877</t>
+          <t>257386</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,2%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>22854</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>17974</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>19997</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>35166</t>
+          <t>37545</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9601</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9730</t>
+          <t>9395</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>19109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>21277</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35053</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,4%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14397</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24414</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13640</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>22778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31023</t>
+          <t>30879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44063</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>63,64%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10081</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23619</t>
+          <t>23791</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26542</t>
+          <t>26415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40235</t>
+          <t>40345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11166</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20828</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>19498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24222</t>
+          <t>24639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37706</t>
+          <t>38306</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>56,58%</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19802</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>19377</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32316</t>
+          <t>32711</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,98%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>21389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31313</t>
+          <t>31719</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21629</t>
+          <t>22074</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37336</t>
+          <t>37485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51071</t>
+          <t>50757</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>756</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>36434</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39112</t>
+          <t>38660</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55424</t>
+          <t>54749</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65162</t>
+          <t>65522</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87776</t>
+          <t>87061</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45398</t>
+          <t>45698</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60398</t>
+          <t>60242</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34099</t>
+          <t>35040</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50471</t>
+          <t>51716</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>84310</t>
+          <t>84341</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>107242</t>
+          <t>105929</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,1%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>14789</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21223</t>
+          <t>21558</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35468</t>
+          <t>35168</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23820</t>
+          <t>24700</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37486</t>
+          <t>37719</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49401</t>
+          <t>49370</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>68919</t>
+          <t>69783</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,35%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>35278</t>
+          <t>35444</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49203</t>
+          <t>48864</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30827</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44713</t>
+          <t>44775</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>70566</t>
+          <t>69350</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>90506</t>
+          <t>89403</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,66%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8640</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12313</t>
+          <t>12554</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21828</t>
+          <t>22176</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17606</t>
+          <t>17700</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>29858</t>
+          <t>30022</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,63%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9839</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11251</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20748</t>
+          <t>20813</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>23504</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35831</t>
+          <t>35752</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,49%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,47 +9391,47 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>23,76%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>4087</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>1150</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>4388</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>562</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>92276</t>
+          <t>92283</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>119503</t>
+          <t>118114</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>124082</t>
+          <t>125371</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>153263</t>
+          <t>152623</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>224277</t>
+          <t>224034</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>265139</t>
+          <t>263781</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>157616</t>
+          <t>159353</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>185624</t>
+          <t>186600</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>133670</t>
+          <t>131807</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>163155</t>
+          <t>160162</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>297707</t>
+          <t>300355</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>339085</t>
+          <t>341010</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>20761</t>
+          <t>20720</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>21301</t>
+          <t>21067</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>37665</t>
+          <t>38007</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14427</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23521</t>
+          <t>23564</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>15393</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25837</t>
+          <t>25553</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32423</t>
+          <t>33658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45712</t>
+          <t>46192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,95%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19269</t>
+          <t>18958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19109</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32480</t>
+          <t>31922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28667</t>
+          <t>29181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27949</t>
+          <t>28413</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38678</t>
+          <t>38726</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49812</t>
+          <t>48677</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65291</t>
+          <t>65399</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>18052</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29291</t>
+          <t>29671</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16927</t>
+          <t>17155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27277</t>
+          <t>28022</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42900</t>
+          <t>43721</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>691</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>13524</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23815</t>
+          <t>23361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39025</t>
+          <t>39336</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,31%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>14458</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>15702</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24067</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37503</t>
+          <t>37207</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,16%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>600</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43109</t>
+          <t>42820</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61729</t>
+          <t>60112</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45460</t>
+          <t>45820</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62873</t>
+          <t>61592</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93931</t>
+          <t>93823</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>118271</t>
+          <t>118693</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,5%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39220</t>
+          <t>40979</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>58057</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28824</t>
+          <t>29559</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45873</t>
+          <t>45144</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74639</t>
+          <t>73412</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>98457</t>
+          <t>98519</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>14808</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22420</t>
+          <t>23524</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28036</t>
+          <t>27527</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41925</t>
+          <t>42530</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26500</t>
+          <t>26507</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40847</t>
+          <t>40571</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>58078</t>
+          <t>57691</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>79057</t>
+          <t>77671</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>53,84%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25730</t>
+          <t>24851</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39297</t>
+          <t>39862</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22610</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36824</t>
+          <t>37095</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>51028</t>
+          <t>52812</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71964</t>
+          <t>72534</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21297</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>18275</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>28224</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>33075</t>
+          <t>33572</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>46247</t>
+          <t>47172</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>18632</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>21708</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35917</t>
+          <t>35377</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,17%</t>
         </is>
       </c>
     </row>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>144238</t>
+          <t>144781</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>175903</t>
+          <t>175601</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>168557</t>
+          <t>168543</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>198430</t>
+          <t>198969</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>322786</t>
+          <t>321753</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>364812</t>
+          <t>365864</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>127814</t>
+          <t>126882</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>157060</t>
+          <t>157221</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>110652</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>140535</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>247077</t>
+          <t>247485</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>290330</t>
+          <t>290434</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,05%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>13539</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>27108</t>
+          <t>27516</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11835</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>25286</t>
+          <t>26627</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>28174</t>
+          <t>29097</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>47969</t>
+          <t>48349</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>891</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7945</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
